--- a/static/data/exports/Retro_OR_GE_2014.xlsx
+++ b/static/data/exports/Retro_OR_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="Q216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>21</v>
@@ -14403,7 +14403,7 @@
         </is>
       </c>
       <c r="Q225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>21</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="Q234" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
         <v>21</v>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="Q244" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
         <v>21</v>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="Q253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>21</v>
@@ -16759,7 +16759,7 @@
         </is>
       </c>
       <c r="Q263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
         <v>21</v>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="Q270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R270" t="n">
         <v>21</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="Q280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R280" t="n">
         <v>21</v>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="Q290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
         <v>21</v>
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="Q300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>21</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="Q310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R310" t="n">
         <v>21</v>
@@ -20231,7 +20231,7 @@
         </is>
       </c>
       <c r="Q319" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R319" t="n">
         <v>21</v>
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="Q340" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R340" t="n">
         <v>21</v>
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="Q350" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R350" t="n">
         <v>21</v>
@@ -30771,7 +30771,7 @@
         </is>
       </c>
       <c r="Q489" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R489" t="n">
         <v>21</v>
@@ -31391,7 +31391,7 @@
         </is>
       </c>
       <c r="Q499" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R499" t="n">
         <v>21</v>
@@ -32011,7 +32011,7 @@
         </is>
       </c>
       <c r="Q509" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R509" t="n">
         <v>21</v>
@@ -32631,7 +32631,7 @@
         </is>
       </c>
       <c r="Q519" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R519" t="n">
         <v>21</v>
@@ -33251,7 +33251,7 @@
         </is>
       </c>
       <c r="Q529" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R529" t="n">
         <v>21</v>
@@ -33871,7 +33871,7 @@
         </is>
       </c>
       <c r="Q539" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R539" t="n">
         <v>21</v>
@@ -34491,7 +34491,7 @@
         </is>
       </c>
       <c r="Q549" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R549" t="n">
         <v>21</v>
@@ -46969,20 +46969,20 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>1285852</v>
+        <v>1285853</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Parameswar Kand</t>
+          <t>Bighna Raj Panda</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>SAMO</t>
+          <t>skd</t>
         </is>
       </c>
       <c r="D751" t="n">
-        <v>15082</v>
+        <v>15087</v>
       </c>
       <c r="E751" t="n">
         <v>525</v>
@@ -47006,12 +47006,12 @@
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>Parameswar Kand</t>
+          <t>Bighna Raj Panda</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
         <is>
-          <t>SAMO</t>
+          <t>skd</t>
         </is>
       </c>
       <c r="Q751" t="b">
@@ -47031,20 +47031,20 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>1285853</v>
+        <v>1285852</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Bighna Raj Panda</t>
+          <t>Parameswar Kand</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>skd</t>
+          <t>SAMO</t>
         </is>
       </c>
       <c r="D752" t="n">
-        <v>15087</v>
+        <v>15082</v>
       </c>
       <c r="E752" t="n">
         <v>525</v>
@@ -47068,12 +47068,12 @@
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>Bighna Raj Panda</t>
+          <t>Parameswar Kand</t>
         </is>
       </c>
       <c r="L752" t="inlineStr">
         <is>
-          <t>skd</t>
+          <t>SAMO</t>
         </is>
       </c>
       <c r="Q752" t="b">
@@ -55075,7 +55075,7 @@
         </is>
       </c>
       <c r="Q881" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R881" t="n">
         <v>21</v>
@@ -55695,7 +55695,7 @@
         </is>
       </c>
       <c r="Q891" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R891" t="n">
         <v>21</v>
@@ -56191,7 +56191,7 @@
         </is>
       </c>
       <c r="Q899" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R899" t="n">
         <v>21</v>
@@ -56749,7 +56749,7 @@
         </is>
       </c>
       <c r="Q908" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R908" t="n">
         <v>21</v>
@@ -57307,7 +57307,7 @@
         </is>
       </c>
       <c r="Q917" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R917" t="n">
         <v>21</v>
@@ -61461,7 +61461,7 @@
         </is>
       </c>
       <c r="Q984" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R984" t="n">
         <v>21</v>
@@ -66111,7 +66111,7 @@
         </is>
       </c>
       <c r="Q1059" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1059" t="n">
         <v>21</v>
@@ -66561,20 +66561,20 @@
     </row>
     <row r="1067">
       <c r="A1067" t="n">
-        <v>1288087</v>
+        <v>1288086</v>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>None Of The Above</t>
+          <t>Ajay Kumar Behera</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="D1067" t="n">
-        <v>15065</v>
+        <v>15064</v>
       </c>
       <c r="E1067" t="n">
         <v>1407</v>
@@ -66598,12 +66598,12 @@
       </c>
       <c r="K1067" t="inlineStr">
         <is>
-          <t>None Of The Above</t>
+          <t>Ajay Kumar Behera</t>
         </is>
       </c>
       <c r="L1067" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="Q1067" t="b">
@@ -66623,20 +66623,20 @@
     </row>
     <row r="1068">
       <c r="A1068" t="n">
-        <v>1288086</v>
+        <v>1288087</v>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>Ajay Kumar Behera</t>
+          <t>None Of The Above</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>CPI</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D1068" t="n">
-        <v>15064</v>
+        <v>15065</v>
       </c>
       <c r="E1068" t="n">
         <v>1407</v>
@@ -66660,16 +66660,16 @@
       </c>
       <c r="K1068" t="inlineStr">
         <is>
-          <t>Ajay Kumar Behera</t>
+          <t>None Of The Above</t>
         </is>
       </c>
       <c r="L1068" t="inlineStr">
         <is>
-          <t>CPI</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="Q1068" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1068" t="n">
         <v>21</v>
@@ -67103,7 +67103,7 @@
         </is>
       </c>
       <c r="Q1075" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1075" t="n">
         <v>21</v>
@@ -67599,7 +67599,7 @@
         </is>
       </c>
       <c r="Q1083" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1083" t="n">
         <v>21</v>
@@ -68095,7 +68095,7 @@
         </is>
       </c>
       <c r="Q1091" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1091" t="n">
         <v>21</v>
@@ -68591,7 +68591,7 @@
         </is>
       </c>
       <c r="Q1099" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1099" t="n">
         <v>21</v>
@@ -77767,7 +77767,7 @@
         </is>
       </c>
       <c r="Q1247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1247" t="n">
         <v>21</v>
@@ -78821,7 +78821,7 @@
         </is>
       </c>
       <c r="Q1264" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1264" t="n">
         <v>21</v>
@@ -79379,7 +79379,7 @@
         </is>
       </c>
       <c r="Q1273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1273" t="n">
         <v>21</v>
@@ -79999,7 +79999,7 @@
         </is>
       </c>
       <c r="Q1283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1283" t="n">
         <v>21</v>
@@ -80619,7 +80619,7 @@
         </is>
       </c>
       <c r="Q1293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1293" t="n">
         <v>21</v>
@@ -81983,7 +81983,7 @@
         </is>
       </c>
       <c r="Q1315" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1315" t="n">
         <v>21</v>
@@ -82603,7 +82603,7 @@
         </is>
       </c>
       <c r="Q1325" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1325" t="n">
         <v>21</v>
@@ -83223,7 +83223,7 @@
         </is>
       </c>
       <c r="Q1335" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1335" t="n">
         <v>21</v>
@@ -83843,7 +83843,7 @@
         </is>
       </c>
       <c r="Q1345" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1345" t="n">
         <v>21</v>
@@ -88927,7 +88927,7 @@
         </is>
       </c>
       <c r="Q1427" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1427" t="n">
         <v>21</v>
@@ -89547,7 +89547,7 @@
         </is>
       </c>
       <c r="Q1437" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1437" t="n">
         <v>21</v>
@@ -90167,7 +90167,7 @@
         </is>
       </c>
       <c r="Q1447" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1447" t="n">
         <v>21</v>
@@ -90849,7 +90849,7 @@
         </is>
       </c>
       <c r="Q1458" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1458" t="n">
         <v>21</v>
@@ -91965,7 +91965,7 @@
         </is>
       </c>
       <c r="Q1476" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1476" t="n">
         <v>21</v>
@@ -92585,7 +92585,7 @@
         </is>
       </c>
       <c r="Q1486" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1486" t="n">
         <v>21</v>
@@ -93143,7 +93143,7 @@
         </is>
       </c>
       <c r="Q1495" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R1495" t="n">
         <v>21</v>

--- a/static/data/exports/Retro_OR_GE_2014.xlsx
+++ b/static/data/exports/Retro_OR_GE_2014.xlsx
@@ -46969,20 +46969,20 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>1285853</v>
+        <v>1285852</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Bighna Raj Panda</t>
+          <t>Parameswar Kand</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>skd</t>
+          <t>SAMO</t>
         </is>
       </c>
       <c r="D751" t="n">
-        <v>15087</v>
+        <v>15082</v>
       </c>
       <c r="E751" t="n">
         <v>525</v>
@@ -47006,12 +47006,12 @@
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>Bighna Raj Panda</t>
+          <t>Parameswar Kand</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
         <is>
-          <t>skd</t>
+          <t>SAMO</t>
         </is>
       </c>
       <c r="Q751" t="b">
@@ -47031,20 +47031,20 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>1285852</v>
+        <v>1285853</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Parameswar Kand</t>
+          <t>Bighna Raj Panda</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>SAMO</t>
+          <t>skd</t>
         </is>
       </c>
       <c r="D752" t="n">
-        <v>15082</v>
+        <v>15087</v>
       </c>
       <c r="E752" t="n">
         <v>525</v>
@@ -47068,12 +47068,12 @@
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>Parameswar Kand</t>
+          <t>Bighna Raj Panda</t>
         </is>
       </c>
       <c r="L752" t="inlineStr">
         <is>
-          <t>SAMO</t>
+          <t>skd</t>
         </is>
       </c>
       <c r="Q752" t="b">
@@ -58262,11 +58262,11 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D933" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E933" t="n">
         <v>599</v>
@@ -59130,11 +59130,11 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D947" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E947" t="n">
         <v>236</v>
@@ -59750,11 +59750,11 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D957" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E957" t="n">
         <v>209</v>
@@ -60494,11 +60494,11 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D969" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E969" t="n">
         <v>114</v>
@@ -61176,11 +61176,11 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D980" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E980" t="n">
         <v>142</v>
@@ -62354,11 +62354,11 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D999" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E999" t="n">
         <v>145</v>
@@ -71530,11 +71530,11 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1147" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1147" t="n">
         <v>125</v>
@@ -72212,11 +72212,11 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1158" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1158" t="n">
         <v>48</v>
@@ -72894,11 +72894,11 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1169" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1169" t="n">
         <v>154</v>
@@ -73700,11 +73700,11 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1182" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1182" t="n">
         <v>88</v>
@@ -74506,11 +74506,11 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1195" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1195" t="n">
         <v>230</v>
@@ -75250,11 +75250,11 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1207" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1207" t="n">
         <v>168</v>
@@ -75994,11 +75994,11 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1219" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1219" t="n">
         <v>135</v>
@@ -77482,11 +77482,11 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1243" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1243" t="n">
         <v>367</v>
@@ -79714,11 +79714,11 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1279" t="n">
         <v>747</v>
@@ -80458,11 +80458,11 @@
       </c>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1291" t="n">
         <v>879</v>
@@ -81140,11 +81140,11 @@
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1302" t="n">
         <v>591</v>
@@ -81326,11 +81326,11 @@
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1305" t="n">
         <v>24908</v>
@@ -82380,11 +82380,11 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1322" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1322" t="n">
         <v>491</v>
@@ -83124,11 +83124,11 @@
       </c>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1334" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1334" t="n">
         <v>544</v>
@@ -83682,11 +83682,11 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1343" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1343" t="n">
         <v>659</v>
@@ -84364,11 +84364,11 @@
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1354" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1354" t="n">
         <v>449</v>
@@ -84736,11 +84736,11 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1360" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1360" t="n">
         <v>1051</v>
@@ -85480,11 +85480,11 @@
       </c>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1372" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1372" t="n">
         <v>742</v>
@@ -86100,11 +86100,11 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1382" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1382" t="n">
         <v>2485</v>
@@ -86968,11 +86968,11 @@
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1396" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1396" t="n">
         <v>818</v>
@@ -87650,11 +87650,11 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1407" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1407" t="n">
         <v>3317</v>
@@ -88332,11 +88332,11 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1418" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1418" t="n">
         <v>2622</v>
@@ -89448,11 +89448,11 @@
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1436" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1436" t="n">
         <v>995</v>
@@ -90006,11 +90006,11 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1445" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1445" t="n">
         <v>1383</v>
@@ -90626,11 +90626,11 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1455" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1455" t="n">
         <v>1661</v>
@@ -91246,11 +91246,11 @@
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1465" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1465" t="n">
         <v>1937</v>
@@ -92424,11 +92424,11 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1484" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1484" t="n">
         <v>683</v>
@@ -92982,11 +92982,11 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1493" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1493" t="n">
         <v>1093</v>
@@ -93602,11 +93602,11 @@
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1503" t="n">
-        <v>15097</v>
+        <v>15110</v>
       </c>
       <c r="E1503" t="n">
         <v>1856</v>
